--- a/wheat_contest_entries.xlsx
+++ b/wheat_contest_entries.xlsx
@@ -42,7 +42,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -104,8 +104,13 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -127,11 +132,55 @@
         <color rgb="00AAAAAA"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -164,6 +213,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -531,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -599,36 +653,78 @@
           <t>Producer / Agent Info</t>
         </is>
       </c>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="12" t="n"/>
+      <c r="K2" s="12" t="n"/>
+      <c r="L2" s="12" t="n"/>
+      <c r="M2" s="12" t="n"/>
+      <c r="N2" s="13" t="n"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Agronomic Data</t>
         </is>
       </c>
+      <c r="P2" s="12" t="n"/>
+      <c r="Q2" s="12" t="n"/>
+      <c r="R2" s="12" t="n"/>
+      <c r="S2" s="12" t="n"/>
+      <c r="T2" s="13" t="n"/>
       <c r="U2" s="4" t="inlineStr">
         <is>
           <t>Fertilizer</t>
         </is>
       </c>
+      <c r="V2" s="12" t="n"/>
+      <c r="W2" s="12" t="n"/>
+      <c r="X2" s="12" t="n"/>
+      <c r="Y2" s="12" t="n"/>
+      <c r="Z2" s="12" t="n"/>
+      <c r="AA2" s="12" t="n"/>
+      <c r="AB2" s="12" t="n"/>
+      <c r="AC2" s="12" t="n"/>
+      <c r="AD2" s="12" t="n"/>
+      <c r="AE2" s="12" t="n"/>
+      <c r="AF2" s="13" t="n"/>
       <c r="AG2" s="5" t="inlineStr">
         <is>
           <t>Pest Management</t>
         </is>
       </c>
+      <c r="AH2" s="12" t="n"/>
+      <c r="AI2" s="12" t="n"/>
+      <c r="AJ2" s="12" t="n"/>
+      <c r="AK2" s="12" t="n"/>
+      <c r="AL2" s="13" t="n"/>
       <c r="AM2" s="6" t="inlineStr">
         <is>
           <t>Harvest Area</t>
         </is>
       </c>
+      <c r="AN2" s="12" t="n"/>
+      <c r="AO2" s="12" t="n"/>
+      <c r="AP2" s="13" t="n"/>
       <c r="AQ2" s="7" t="inlineStr">
         <is>
           <t>Grain Characteristics</t>
         </is>
       </c>
+      <c r="AR2" s="12" t="n"/>
+      <c r="AS2" s="12" t="n"/>
+      <c r="AT2" s="12" t="n"/>
+      <c r="AU2" s="13" t="n"/>
       <c r="AV2" s="8" t="inlineStr">
         <is>
           <t>Yield Calculation</t>
         </is>
       </c>
+      <c r="AW2" s="13" t="n"/>
       <c r="AX2" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
@@ -893,12 +989,12 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>2026-09-25 15:57</t>
+          <t>2026-09-25 16:58</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Fayette</t>
+          <t>Campbell</t>
         </is>
       </c>
       <c r="D4" s="11" t="n">
@@ -906,31 +1002,15 @@
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>John Doe</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Shamim</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Lexington</t>
-        </is>
-      </c>
+          <t>Mohammad Jan</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr"/>
+      <c r="G4" s="11" t="inlineStr"/>
       <c r="H4" s="11" t="inlineStr"/>
       <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>8595391251</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>M Farms</t>
-        </is>
-      </c>
+      <c r="J4" s="11" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr"/>
       <c r="L4" s="11" t="inlineStr">
         <is>
           <t>2026-09-25</t>
@@ -938,7 +1018,7 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>Mohammad</t>
+          <t>Mohammad J. Shamim</t>
         </is>
       </c>
       <c r="N4" s="11" t="inlineStr">
@@ -948,7 +1028,7 @@
       </c>
       <c r="O4" s="11" t="inlineStr">
         <is>
-          <t>Division II - No-Tillage</t>
+          <t>Division I - Tillage (conv./min.)</t>
         </is>
       </c>
       <c r="P4" s="11" t="inlineStr">
@@ -963,19 +1043,11 @@
       </c>
       <c r="R4" s="11" t="inlineStr">
         <is>
-          <t>xmt</t>
-        </is>
-      </c>
-      <c r="S4" s="11" t="inlineStr">
-        <is>
-          <t>7.05</t>
-        </is>
-      </c>
-      <c r="T4" s="11" t="inlineStr">
-        <is>
-          <t>1800000</t>
-        </is>
-      </c>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="S4" s="11" t="inlineStr"/>
+      <c r="T4" s="11" t="inlineStr"/>
       <c r="U4" s="11" t="inlineStr">
         <is>
           <t>0</t>
@@ -1027,37 +1099,181 @@
       <c r="AK4" s="11" t="inlineStr"/>
       <c r="AL4" s="11" t="inlineStr"/>
       <c r="AM4" s="11" t="n">
-        <v>300</v>
+        <v>2200</v>
       </c>
       <c r="AN4" s="11" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AO4" s="11" t="n">
-        <v>90000</v>
+        <v>440000</v>
       </c>
       <c r="AP4" s="11" t="n">
-        <v>2.0661</v>
+        <v>10.101</v>
       </c>
       <c r="AQ4" s="11" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AR4" s="11" t="n">
-        <v>13.5</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="AR4" s="11" t="inlineStr"/>
       <c r="AS4" s="11" t="inlineStr"/>
       <c r="AT4" s="11" t="n">
-        <v>13.45</v>
+        <v>12</v>
       </c>
       <c r="AU4" s="11" t="n">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="AV4" s="11" t="n">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="AW4" s="11" t="n">
-        <v>121.07</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="AX4" s="11" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:22</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Campbell</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Mohammad Jan</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr"/>
+      <c r="H5" s="14" t="inlineStr"/>
+      <c r="I5" s="14" t="inlineStr"/>
+      <c r="J5" s="14" t="inlineStr"/>
+      <c r="K5" s="14" t="inlineStr"/>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>Mohammad J. Shamim</t>
+        </is>
+      </c>
+      <c r="N5" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="O5" s="14" t="inlineStr">
+        <is>
+          <t>Division I - Tillage (conv./min.)</t>
+        </is>
+      </c>
+      <c r="P5" s="14" t="inlineStr">
+        <is>
+          <t>Corn</t>
+        </is>
+      </c>
+      <c r="Q5" s="14" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="R5" s="14" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="S5" s="14" t="inlineStr"/>
+      <c r="T5" s="14" t="inlineStr"/>
+      <c r="U5" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V5" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" s="14" t="inlineStr"/>
+      <c r="Y5" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="Z5" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA5" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB5" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC5" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD5" s="14" t="inlineStr"/>
+      <c r="AE5" s="14" t="inlineStr"/>
+      <c r="AF5" s="14" t="inlineStr"/>
+      <c r="AG5" s="14" t="inlineStr"/>
+      <c r="AH5" s="14" t="inlineStr"/>
+      <c r="AI5" s="14" t="inlineStr"/>
+      <c r="AJ5" s="14" t="inlineStr"/>
+      <c r="AK5" s="14" t="inlineStr"/>
+      <c r="AL5" s="14" t="inlineStr"/>
+      <c r="AM5" s="14" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AN5" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="AO5" s="14" t="n">
+        <v>440000</v>
+      </c>
+      <c r="AP5" s="14" t="n">
+        <v>10.101</v>
+      </c>
+      <c r="AQ5" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR5" s="14" t="inlineStr"/>
+      <c r="AS5" s="14" t="inlineStr"/>
+      <c r="AT5" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU5" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AV5" s="14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AW5" s="14" t="n">
+        <v>83.93000000000001</v>
+      </c>
+      <c r="AX5" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="9">
